--- a/backend/database/seeders/MaestrosTODOS.xlsx
+++ b/backend/database/seeders/MaestrosTODOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\bebrascubarui\api\database\seeders\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\bebrascuba-main\backend\database\seeders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AA1233-F417-43A7-B748-B49E2B6E48D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0102D1-CEE9-4AF0-97B1-94A0365D14EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7296145F-7863-490F-B1A4-B2A29F3DAC4C}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="532">
   <si>
     <t>nombre_teacher</t>
   </si>
@@ -810,9 +810,6 @@
     <t>Miguel Diosdado Pérez Pimentel</t>
   </si>
   <si>
-    <t>Sagua la Grande</t>
-  </si>
-  <si>
     <t>Sagua</t>
   </si>
   <si>
@@ -1282,9 +1279,6 @@
   </si>
   <si>
     <t>Roberto Mederos Rodríguez</t>
-  </si>
-  <si>
-    <t>Sagua La Grande</t>
   </si>
   <si>
     <t>Yulien</t>
@@ -1645,6 +1639,9 @@
   </si>
   <si>
     <t>03012771290</t>
+  </si>
+  <si>
+    <t>Sagua la Grande</t>
   </si>
 </sst>
 </file>
@@ -1719,7 +1716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1779,9 +1776,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2556,7 +2550,7 @@
         <v>84</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E11" s="19">
         <v>52800004</v>
@@ -3264,7 +3258,7 @@
         <v>195</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="7" t="s">
@@ -3783,10 +3777,10 @@
         <v>29</v>
       </c>
       <c r="L38" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="M38" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="N38" s="9">
         <v>42662381</v>
@@ -3797,13 +3791,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="D39" s="8">
         <v>62040804652</v>
@@ -3812,19 +3806,19 @@
         <v>55532580</v>
       </c>
       <c r="F39" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G39" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H39" s="7" t="s">
         <v>260</v>
-      </c>
-      <c r="G39" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>261</v>
       </c>
       <c r="I39" s="8">
         <v>26090122</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>29</v>
@@ -3851,13 +3845,13 @@
         <v>84</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E40" s="8">
         <v>52800004</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G40" s="9">
         <v>1234</v>
@@ -3885,13 +3879,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="D41" s="8">
         <v>72032822610</v>
@@ -3900,28 +3894,28 @@
         <v>53942422</v>
       </c>
       <c r="F41" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="G41" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H41" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="G41" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H41" s="7" t="s">
+      <c r="I41" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="J41" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="K41" s="7" t="s">
         <v>270</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>144</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N41" s="9">
         <v>42399784</v>
@@ -3932,13 +3926,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>274</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>275</v>
       </c>
       <c r="D42" s="8">
         <v>68123104052</v>
@@ -3947,28 +3941,28 @@
         <v>59742892</v>
       </c>
       <c r="F42" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G42" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="G42" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H42" s="7" t="s">
+      <c r="I42" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="J42" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="J42" s="7" t="s">
-        <v>279</v>
-      </c>
       <c r="K42" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>144</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N42" s="9">
         <v>42384534</v>
@@ -3979,13 +3973,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>283</v>
       </c>
       <c r="D43" s="8">
         <v>65112103290</v>
@@ -3994,19 +3988,19 @@
         <v>53767723</v>
       </c>
       <c r="F43" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G43" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="G43" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H43" s="7" t="s">
+      <c r="I43" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="J43" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>287</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>53</v>
@@ -4015,7 +4009,7 @@
         <v>46</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N43" s="9">
         <v>42271692</v>
@@ -4026,13 +4020,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>291</v>
       </c>
       <c r="D44" s="8">
         <v>70052508856</v>
@@ -4041,19 +4035,19 @@
         <v>53425618</v>
       </c>
       <c r="F44" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="G44" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H44" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="G44" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H44" s="7" t="s">
+      <c r="I44" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="J44" s="7" t="s">
         <v>294</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>295</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>37</v>
@@ -4073,13 +4067,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>298</v>
       </c>
       <c r="D45" s="8">
         <v>72050309791</v>
@@ -4088,7 +4082,7 @@
         <v>56405648</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G45" s="9">
         <v>1234</v>
@@ -4104,7 +4098,7 @@
         <v>53</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="9">
@@ -4131,7 +4125,7 @@
         <v>52457795</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G46" s="9">
         <v>1234</v>
@@ -4159,36 +4153,36 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>304</v>
-      </c>
       <c r="D47" s="8" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G47" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="G47" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>306</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>37</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="9"/>
@@ -4198,13 +4192,13 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>310</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>311</v>
       </c>
       <c r="D48" s="8">
         <v>73090117840</v>
@@ -4213,28 +4207,28 @@
         <v>55693544</v>
       </c>
       <c r="F48" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G48" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="G48" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H48" s="7" t="s">
+      <c r="I48" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="J48" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="K48" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="L48" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="L48" s="10" t="s">
-        <v>317</v>
-      </c>
       <c r="M48" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N48" s="9">
         <v>42686584</v>
@@ -4245,13 +4239,13 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>320</v>
       </c>
       <c r="D49" s="8">
         <v>75020117111</v>
@@ -4260,17 +4254,17 @@
         <v>53981312</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="G49" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="G49" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>322</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>53</v>
@@ -4288,13 +4282,13 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>326</v>
       </c>
       <c r="D50" s="8">
         <v>81081521537</v>
@@ -4303,7 +4297,7 @@
         <v>52654065</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G50" s="9">
         <v>1234</v>
@@ -4319,7 +4313,7 @@
         <v>29</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="9">
@@ -4331,13 +4325,13 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>331</v>
       </c>
       <c r="D51" s="8">
         <v>83042816341</v>
@@ -4346,23 +4340,23 @@
         <v>54158150</v>
       </c>
       <c r="F51" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G51" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H51" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="G51" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="9">
@@ -4374,13 +4368,13 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="C52" s="7" t="s">
         <v>337</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>338</v>
       </c>
       <c r="D52" s="8">
         <v>94072304583</v>
@@ -4389,23 +4383,23 @@
         <v>55807479</v>
       </c>
       <c r="F52" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G52" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H52" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="G52" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>340</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>37</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="9">
@@ -4417,13 +4411,13 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="D53" s="8">
         <v>76101026995</v>
@@ -4432,19 +4426,19 @@
         <v>55737639</v>
       </c>
       <c r="F53" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="G53" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="G53" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H53" s="7" t="s">
+      <c r="I53" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="J53" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>349</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>29</v>
@@ -4464,13 +4458,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="C54" s="7" t="s">
         <v>351</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>352</v>
       </c>
       <c r="D54" s="8">
         <v>76031927293</v>
@@ -4479,19 +4473,19 @@
         <v>56097642</v>
       </c>
       <c r="F54" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G54" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H54" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G54" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H54" s="7" t="s">
+      <c r="I54" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="J54" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>356</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>29</v>
@@ -4524,7 +4518,7 @@
         <v>56215648</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G55" s="9">
         <v>1234</v>
@@ -4552,13 +4546,13 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>360</v>
       </c>
       <c r="D56" s="8">
         <v>82092305016</v>
@@ -4567,17 +4561,17 @@
         <v>54335218</v>
       </c>
       <c r="F56" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G56" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H56" s="7" t="s">
         <v>361</v>
-      </c>
-      <c r="G56" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>362</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>29</v>
@@ -4595,36 +4589,36 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="C57" s="7" t="s">
-        <v>366</v>
-      </c>
       <c r="D57" s="8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G57" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H57" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="G57" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>368</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>53</v>
       </c>
       <c r="L57" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="9"/>
@@ -4634,34 +4628,34 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>373</v>
-      </c>
       <c r="D58" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E58" s="9">
         <v>55734674</v>
       </c>
       <c r="F58" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G58" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H58" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G58" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H58" s="7" t="s">
+      <c r="I58" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="J58" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>377</v>
       </c>
       <c r="K58" s="7" t="s">
         <v>53</v>
@@ -4679,32 +4673,32 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>380</v>
-      </c>
       <c r="D59" s="8" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G59" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H59" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="G59" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H59" s="7" t="s">
+      <c r="I59" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="J59" s="7" t="s">
         <v>383</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>384</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>53</v>
@@ -4722,13 +4716,13 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="D60" s="8">
         <v>87050135315</v>
@@ -4737,23 +4731,23 @@
         <v>52465767</v>
       </c>
       <c r="F60" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="G60" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H60" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="G60" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>389</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K60" s="7" t="s">
         <v>45</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="9">
@@ -4780,17 +4774,17 @@
         <v>59966488</v>
       </c>
       <c r="F61" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="G61" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H61" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="G61" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>229</v>
@@ -4808,36 +4802,36 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="C62" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>395</v>
-      </c>
       <c r="D62" s="8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E62" s="9"/>
       <c r="F62" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G62" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H62" s="7" t="s">
         <v>396</v>
-      </c>
-      <c r="G62" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>397</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K62" s="7" t="s">
         <v>29</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="9"/>
@@ -4847,13 +4841,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="C63" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>401</v>
       </c>
       <c r="D63" s="8">
         <v>82030924024</v>
@@ -4862,23 +4856,23 @@
         <v>31549910</v>
       </c>
       <c r="F63" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="G63" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>402</v>
-      </c>
-      <c r="G63" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>403</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>29</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="9">
@@ -4890,13 +4884,13 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B64" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>407</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>408</v>
       </c>
       <c r="D64" s="8">
         <v>76111406650</v>
@@ -4905,28 +4899,28 @@
         <v>51023089</v>
       </c>
       <c r="F64" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G64" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="G64" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H64" s="7" t="s">
+      <c r="I64" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="I64" s="8" t="s">
+      <c r="J64" s="7" t="s">
         <v>411</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>412</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>182</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>413</v>
+        <v>531</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N64" s="9">
         <v>42662558</v>
@@ -4937,32 +4931,32 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B65" s="7"/>
       <c r="C65" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E65" s="9">
         <v>58492168</v>
       </c>
       <c r="F65" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="G65" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="I65" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="G65" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H65" s="7" t="s">
+      <c r="J65" s="7" t="s">
         <v>417</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>419</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>29</v>
@@ -4982,32 +4976,32 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>422</v>
-      </c>
       <c r="D66" s="8" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E66" s="9"/>
       <c r="F66" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="G66" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="I66" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="G66" s="9">
-        <v>1234</v>
-      </c>
-      <c r="H66" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>426</v>
       </c>
       <c r="K66" s="7" t="s">
         <v>29</v>
@@ -5023,30 +5017,30 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="C67" s="13" t="s">
         <v>427</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>429</v>
       </c>
       <c r="D67" s="14">
         <v>77777777777</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G67" s="14">
         <v>1234</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="15" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K67" s="15" t="s">
         <v>29</v>
@@ -5077,7 +5071,7 @@
         <v>52488305</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G68" s="14">
         <v>1234</v>
@@ -5107,34 +5101,34 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="D69" s="16" t="s">
         <v>434</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>436</v>
       </c>
       <c r="E69" s="14">
         <v>52838409</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G69" s="14">
         <v>1234</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I69" s="16">
         <v>26090121</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K69" s="15" t="s">
         <v>29</v>
@@ -5154,34 +5148,34 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="D70" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="E70" s="16" t="s">
         <v>442</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="F70" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="E70" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>445</v>
-      </c>
       <c r="G70" s="14">
         <v>1234</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I70" s="16">
         <v>26090122</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K70" s="15" t="s">
         <v>29</v>
@@ -5190,7 +5184,7 @@
         <v>46</v>
       </c>
       <c r="M70" s="13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N70" s="14">
         <v>42203824</v>
@@ -5201,13 +5195,13 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="C71" s="13" t="s">
         <v>386</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>387</v>
       </c>
       <c r="D71" s="16">
         <v>87050135315</v>
@@ -5216,23 +5210,23 @@
         <v>52465767</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G71" s="14">
         <v>1234</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I71" s="16"/>
       <c r="J71" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K71" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M71" s="13"/>
       <c r="N71" s="14">
@@ -5250,7 +5244,7 @@
         <v>208</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D72" s="16">
         <v>89051629454</v>
@@ -5259,7 +5253,7 @@
         <v>51060663</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G72" s="14">
         <v>1234</v>
@@ -5291,34 +5285,34 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="D73" s="16" t="s">
         <v>453</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>455</v>
       </c>
       <c r="E73" s="14">
         <v>56099939</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G73" s="14">
         <v>1234</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I73" s="16" t="s">
         <v>247</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K73" s="15" t="s">
         <v>29</v>
@@ -5338,30 +5332,30 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="B74" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>460</v>
-      </c>
       <c r="D74" s="16" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E74" s="14"/>
       <c r="F74" s="13" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G74" s="14">
         <v>1234</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I74" s="16"/>
       <c r="J74" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K74" s="15" t="s">
         <v>29</v>
@@ -5377,32 +5371,32 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="D75" s="16" t="s">
         <v>464</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>466</v>
       </c>
       <c r="E75" s="14">
         <v>58218692</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G75" s="14">
         <v>1234</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I75" s="16"/>
       <c r="J75" s="13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K75" s="15" t="s">
         <v>229</v>
@@ -5435,13 +5429,13 @@
         <v>58408112</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G76" s="14">
         <v>1234</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I76" s="16"/>
       <c r="J76" s="13" t="s">
@@ -5463,13 +5457,13 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B77" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="C77" s="13" t="s">
         <v>310</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>311</v>
       </c>
       <c r="D77" s="16">
         <v>73090117840</v>
@@ -5478,28 +5472,28 @@
         <v>55693544</v>
       </c>
       <c r="F77" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="G77" s="14">
+        <v>1234</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="I77" s="16" t="s">
         <v>471</v>
       </c>
-      <c r="G77" s="14">
-        <v>1234</v>
-      </c>
-      <c r="H77" s="13" t="s">
+      <c r="J77" s="13" t="s">
         <v>472</v>
-      </c>
-      <c r="I77" s="16" t="s">
-        <v>473</v>
-      </c>
-      <c r="J77" s="13" t="s">
-        <v>474</v>
       </c>
       <c r="K77" s="15" t="s">
         <v>29</v>
       </c>
       <c r="L77" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M77" s="13" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N77" s="14">
         <v>42686584</v>
@@ -5525,7 +5519,7 @@
         <v>56097769</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G78" s="14">
         <v>1234</v>
@@ -5557,26 +5551,26 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C79" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="B79" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>479</v>
-      </c>
       <c r="D79" s="16" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E79" s="14"/>
       <c r="F79" s="13" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G79" s="14">
         <v>1234</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I79" s="16"/>
       <c r="J79" s="13" t="s">
@@ -5607,13 +5601,13 @@
         <v>84</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E80" s="16">
         <v>52800004</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G80" s="14">
         <v>1234</v>
@@ -5656,7 +5650,7 @@
         <v>56983180</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G81" s="14">
         <v>1234</v>
@@ -5688,30 +5682,30 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="C82" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="B82" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>486</v>
-      </c>
       <c r="D82" s="16" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E82" s="14"/>
       <c r="F82" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G82" s="14">
         <v>1234</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I82" s="16"/>
       <c r="J82" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K82" s="15" t="s">
         <v>29</v>
@@ -5727,32 +5721,32 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="D83" s="16" t="s">
         <v>488</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>490</v>
       </c>
       <c r="E83" s="14">
         <v>58343482</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G83" s="14">
         <v>1234</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I83" s="16"/>
       <c r="J83" s="13" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K83" s="15" t="s">
         <v>29</v>
@@ -5770,13 +5764,13 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B84" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="C84" s="13" t="s">
         <v>282</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>283</v>
       </c>
       <c r="D84" s="16">
         <v>65112103290</v>
@@ -5785,19 +5779,19 @@
         <v>53767723</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G84" s="14">
         <v>1234</v>
       </c>
       <c r="H84" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="I84" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="I84" s="16" t="s">
+      <c r="J84" s="13" t="s">
         <v>286</v>
-      </c>
-      <c r="J84" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="K84" s="15" t="s">
         <v>53</v>
@@ -5806,7 +5800,7 @@
         <v>46</v>
       </c>
       <c r="M84" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N84" s="14">
         <v>42271692</v>
@@ -5832,7 +5826,7 @@
         <v>59056645</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G85" s="14">
         <v>1234</v>
@@ -5879,17 +5873,17 @@
         <v>59966488</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G86" s="14">
         <v>1234</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I86" s="16"/>
       <c r="J86" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K86" s="15" t="s">
         <v>229</v>
@@ -5907,22 +5901,22 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="C87" s="13" t="s">
         <v>496</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>498</v>
       </c>
       <c r="D87" s="16">
         <v>82022313811</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G87" s="14">
         <v>1234</v>
@@ -5969,7 +5963,7 @@
         <v>53074481</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G88" s="14">
         <v>1234</v>
@@ -6001,13 +5995,13 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="C89" s="13" t="s">
         <v>502</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>504</v>
       </c>
       <c r="D89" s="16">
         <v>60010606092</v>
@@ -6016,19 +6010,19 @@
         <v>53732555</v>
       </c>
       <c r="F89" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="G89" s="14">
+        <v>1234</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="I89" s="16" t="s">
         <v>505</v>
       </c>
-      <c r="G89" s="14">
-        <v>1234</v>
-      </c>
-      <c r="H89" s="13" t="s">
+      <c r="J89" s="13" t="s">
         <v>506</v>
-      </c>
-      <c r="I89" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="J89" s="13" t="s">
-        <v>508</v>
       </c>
       <c r="K89" s="15" t="s">
         <v>37</v>
@@ -6040,7 +6034,7 @@
         <v>241</v>
       </c>
       <c r="N89" s="16" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="O89" s="14">
         <v>2024</v>
@@ -6048,36 +6042,36 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="C90" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>304</v>
-      </c>
       <c r="D90" s="16" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E90" s="16"/>
       <c r="F90" s="13" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G90" s="14">
         <v>1234</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I90" s="16"/>
       <c r="J90" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K90" s="15" t="s">
         <v>37</v>
       </c>
       <c r="L90" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M90" s="13"/>
       <c r="N90" s="14"/>
@@ -6087,13 +6081,13 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B91" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="C91" s="13" t="s">
         <v>359</v>
-      </c>
-      <c r="C91" s="27" t="s">
-        <v>360</v>
       </c>
       <c r="D91" s="16">
         <v>82092305016</v>
@@ -6102,17 +6096,17 @@
         <v>54335218</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G91" s="14">
         <v>1234</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I91" s="16"/>
       <c r="J91" s="13" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K91" s="15" t="s">
         <v>37</v>
@@ -6143,7 +6137,7 @@
         <v>54403951</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G92" s="14">
         <v>1234</v>
@@ -6171,26 +6165,26 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="C93" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="B93" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>517</v>
-      </c>
       <c r="D93" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E93" s="14"/>
       <c r="F93" s="13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G93" s="14">
         <v>1234</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I93" s="16"/>
       <c r="J93" s="13" t="s">
